--- a/Data/TextFiles/Dialogue.xlsx
+++ b/Data/TextFiles/Dialogue.xlsx
@@ -1261,7 +1261,7 @@
     <x:col min="7" max="7" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:7" ht="6" customHeight="1">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1281,7 +1281,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:7" ht="6" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
@@ -1304,7 +1304,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:7">
+    <x:row r="3" spans="1:7" ht="6" customHeight="1">
       <x:c r="A3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -1327,7 +1327,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:7">
+    <x:row r="4" spans="1:7" ht="6" customHeight="1">
       <x:c r="A4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
@@ -1350,7 +1350,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:7">
+    <x:row r="5" spans="1:7" ht="6" customHeight="1">
       <x:c r="A5" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
@@ -1373,7 +1373,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:7">
+    <x:row r="6" spans="1:7" ht="6" customHeight="1">
       <x:c r="A6" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
@@ -1396,7 +1396,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:7">
+    <x:row r="7" spans="1:7" ht="6" customHeight="1">
       <x:c r="A7" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
@@ -1419,7 +1419,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:7">
+    <x:row r="8" spans="1:7" ht="6" customHeight="1">
       <x:c r="A8" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
@@ -1442,7 +1442,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:7">
+    <x:row r="9" spans="1:7" ht="6" customHeight="1">
       <x:c r="A9" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
@@ -1465,7 +1465,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:7">
+    <x:row r="10" spans="1:7" ht="6" customHeight="1">
       <x:c r="A10" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
@@ -1488,7 +1488,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:7">
+    <x:row r="11" spans="1:7" ht="6" customHeight="1">
       <x:c r="A11" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -1511,7 +1511,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:7">
+    <x:row r="12" spans="1:7" ht="6" customHeight="1">
       <x:c r="A12" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
@@ -1534,7 +1534,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:7">
+    <x:row r="13" spans="1:7" ht="6" customHeight="1">
       <x:c r="A13" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -1557,7 +1557,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:7">
+    <x:row r="14" spans="1:7" ht="6" customHeight="1">
       <x:c r="A14" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
@@ -1580,7 +1580,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:7">
+    <x:row r="15" spans="1:7" ht="6" customHeight="1">
       <x:c r="A15" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
@@ -1603,7 +1603,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:7">
+    <x:row r="16" spans="1:7" ht="6" customHeight="1">
       <x:c r="A16" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
@@ -1626,7 +1626,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:7">
+    <x:row r="17" spans="1:7" ht="6" customHeight="1">
       <x:c r="A17" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
@@ -1649,7 +1649,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:7">
+    <x:row r="18" spans="1:7" ht="6" customHeight="1">
       <x:c r="A18" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
@@ -1672,7 +1672,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:7">
+    <x:row r="19" spans="1:7" ht="6" customHeight="1">
       <x:c r="A19" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -1695,7 +1695,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:7">
+    <x:row r="20" spans="1:7" ht="6" customHeight="1">
       <x:c r="A20" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
@@ -1718,7 +1718,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:7">
+    <x:row r="21" spans="1:7" ht="6" customHeight="1">
       <x:c r="A21" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -1741,7 +1741,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:7">
+    <x:row r="22" spans="1:7" ht="6" customHeight="1">
       <x:c r="A22" s="0" t="s">
         <x:v>127</x:v>
       </x:c>
@@ -1764,7 +1764,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:7">
+    <x:row r="23" spans="1:7" ht="6" customHeight="1">
       <x:c r="A23" s="0" t="s">
         <x:v>133</x:v>
       </x:c>
@@ -1787,7 +1787,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:7">
+    <x:row r="24" spans="1:7" ht="6" customHeight="1">
       <x:c r="A24" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
@@ -1810,7 +1810,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:7">
+    <x:row r="25" spans="1:7" ht="6" customHeight="1">
       <x:c r="A25" s="0" t="s">
         <x:v>145</x:v>
       </x:c>
@@ -1833,7 +1833,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:7">
+    <x:row r="26" spans="1:7" ht="6" customHeight="1">
       <x:c r="A26" s="0" t="s">
         <x:v>151</x:v>
       </x:c>
@@ -1856,7 +1856,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:7">
+    <x:row r="27" spans="1:7" ht="6" customHeight="1">
       <x:c r="A27" s="0" t="s">
         <x:v>157</x:v>
       </x:c>
@@ -1879,7 +1879,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:7">
+    <x:row r="28" spans="1:7" ht="6" customHeight="1">
       <x:c r="A28" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
@@ -1902,7 +1902,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:7">
+    <x:row r="29" spans="1:7" ht="6" customHeight="1">
       <x:c r="A29" s="0" t="s">
         <x:v>169</x:v>
       </x:c>
@@ -1925,7 +1925,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:7">
+    <x:row r="30" spans="1:7" ht="6" customHeight="1">
       <x:c r="A30" s="0" t="s">
         <x:v>175</x:v>
       </x:c>
@@ -1948,7 +1948,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:7">
+    <x:row r="31" spans="1:7" ht="6" customHeight="1">
       <x:c r="A31" s="0" t="s">
         <x:v>181</x:v>
       </x:c>
@@ -1971,7 +1971,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:7">
+    <x:row r="32" spans="1:7" ht="6" customHeight="1">
       <x:c r="A32" s="0" t="s">
         <x:v>187</x:v>
       </x:c>
@@ -1994,7 +1994,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:7">
+    <x:row r="33" spans="1:7" ht="6" customHeight="1">
       <x:c r="A33" s="0" t="s">
         <x:v>193</x:v>
       </x:c>
@@ -2017,7 +2017,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:7">
+    <x:row r="34" spans="1:7" ht="6" customHeight="1">
       <x:c r="A34" s="0" t="s">
         <x:v>199</x:v>
       </x:c>
@@ -2040,7 +2040,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:7">
+    <x:row r="35" spans="1:7" ht="6" customHeight="1">
       <x:c r="A35" s="0" t="s">
         <x:v>205</x:v>
       </x:c>
@@ -2063,7 +2063,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:7">
+    <x:row r="36" spans="1:7" ht="6" customHeight="1">
       <x:c r="A36" s="0" t="s">
         <x:v>211</x:v>
       </x:c>
@@ -2086,7 +2086,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:7">
+    <x:row r="37" spans="1:7" ht="6" customHeight="1">
       <x:c r="A37" s="0" t="s">
         <x:v>217</x:v>
       </x:c>
@@ -2109,7 +2109,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:7">
+    <x:row r="38" spans="1:7" ht="6" customHeight="1">
       <x:c r="A38" s="0" t="s">
         <x:v>223</x:v>
       </x:c>
@@ -2132,7 +2132,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:7">
+    <x:row r="39" spans="1:7" ht="6" customHeight="1">
       <x:c r="A39" s="0" t="s">
         <x:v>229</x:v>
       </x:c>
@@ -2155,7 +2155,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:7">
+    <x:row r="40" spans="1:7" ht="6" customHeight="1">
       <x:c r="A40" s="0" t="s">
         <x:v>235</x:v>
       </x:c>
@@ -2178,7 +2178,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:7">
+    <x:row r="41" spans="1:7" ht="6" customHeight="1">
       <x:c r="A41" s="0" t="s">
         <x:v>241</x:v>
       </x:c>
@@ -2201,7 +2201,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:7">
+    <x:row r="42" spans="1:7" ht="6" customHeight="1">
       <x:c r="A42" s="0" t="s">
         <x:v>247</x:v>
       </x:c>
@@ -2224,7 +2224,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:7">
+    <x:row r="43" spans="1:7" ht="6" customHeight="1">
       <x:c r="A43" s="0" t="s">
         <x:v>253</x:v>
       </x:c>
@@ -2247,7 +2247,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:7">
+    <x:row r="44" spans="1:7" ht="6" customHeight="1">
       <x:c r="A44" s="0" t="s">
         <x:v>259</x:v>
       </x:c>
@@ -2270,7 +2270,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:7">
+    <x:row r="45" spans="1:7" ht="6" customHeight="1">
       <x:c r="A45" s="0" t="s">
         <x:v>265</x:v>
       </x:c>
@@ -2293,7 +2293,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:7">
+    <x:row r="46" spans="1:7" ht="6" customHeight="1">
       <x:c r="A46" s="0" t="s">
         <x:v>271</x:v>
       </x:c>
@@ -2316,7 +2316,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:7">
+    <x:row r="47" spans="1:7" ht="6" customHeight="1">
       <x:c r="A47" s="0" t="s">
         <x:v>277</x:v>
       </x:c>
@@ -2339,7 +2339,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:7">
+    <x:row r="48" spans="1:7" ht="6" customHeight="1">
       <x:c r="A48" s="0" t="s">
         <x:v>283</x:v>
       </x:c>
@@ -2362,7 +2362,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:7">
+    <x:row r="49" spans="1:7" ht="6" customHeight="1">
       <x:c r="A49" s="0" t="s">
         <x:v>289</x:v>
       </x:c>
